--- a/output/pdf_financials_xlsx/FTS.xlsx
+++ b/output/pdf_financials_xlsx/FTS.xlsx
@@ -3502,31 +3502,31 @@
         <v>1517</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>977</v>
+        <v>1305</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>966</v>
+        <v>1350</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>957</v>
+        <v>2084</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>1440</v>
+        <v>2676</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>1419</v>
+        <v>2638</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>1970</v>
+        <v>3944</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>2053</v>
+        <v>3504</v>
       </c>
       <c r="K75" s="3" t="n">
-        <v>2289</v>
+        <v>4252</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>2378</v>
+        <v>4176</v>
       </c>
     </row>
     <row r="76">
@@ -6966,7 +6966,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>OtherCurrentLiabilities</t>
+          <t>CurrentLiabilities</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -8724,7 +8724,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>OtherCurrentLiabilities</t>
+          <t>CurrentLiabilities</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>OtherCurrentLiabilities</t>
+          <t>CurrentLiabilities</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">

--- a/output/pdf_financials_xlsx/FTS.xlsx
+++ b/output/pdf_financials_xlsx/FTS.xlsx
@@ -25064,7 +25064,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">

--- a/output/pdf_financials_xlsx/FTS.xlsx
+++ b/output/pdf_financials_xlsx/FTS.xlsx
@@ -1599,10 +1599,10 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D28" s="3" t="n">
         <v>416</v>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>292</v>
+        <v>335</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>323</v>
+        <v>363</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>866</v>
@@ -1679,10 +1679,10 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>8.015371946198188</v>
+        <v>9.195717814987647</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>8.832376264697841</v>
+        <v>9.92616899097621</v>
       </c>
       <c r="D30" s="3" t="n">
         <v>23.16746923488497</v>
@@ -4505,37 +4505,37 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>1152</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>1213</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="101">
@@ -5545,37 +5545,37 @@
         </is>
       </c>
       <c r="B126" s="3" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="C126" s="3" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="D126" s="3" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="E126" s="3" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="F126" s="3" t="n">
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="G126" s="3" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="H126" s="3" t="n">
-        <v>0</v>
+        <v>-23</v>
       </c>
       <c r="I126" s="3" t="n">
-        <v>0</v>
+        <v>-53</v>
       </c>
       <c r="J126" s="3" t="n">
-        <v>0</v>
+        <v>-109</v>
       </c>
       <c r="K126" s="3" t="n">
-        <v>0</v>
+        <v>-85</v>
       </c>
       <c r="L126" s="3" t="n">
-        <v>0</v>
+        <v>-73</v>
       </c>
     </row>
     <row r="127">
@@ -15373,7 +15373,11 @@
           <t>Depreciation – property, plant and equipment</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr"/>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E138" t="inlineStr">
         <is>
           <t>-</t>
@@ -15438,7 +15442,11 @@
           <t>Amortization – intangible assets</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr"/>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E139" t="inlineStr">
         <is>
           <t>-</t>
@@ -16899,7 +16907,11 @@
           <t>Subsidiary dividends paid to non-controlling interests</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr"/>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>CashDividendsPaid</t>
+        </is>
+      </c>
       <c r="E162" s="5" t="n">
         <v>-10</v>
       </c>
@@ -18737,7 +18749,11 @@
           <t>Amortization – intangible assets</t>
         </is>
       </c>
-      <c r="D190" t="inlineStr"/>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E190" t="inlineStr">
         <is>
           <t>-</t>
@@ -23432,7 +23448,11 @@
           <t>Amortization – intangible assets</t>
         </is>
       </c>
-      <c r="D259" t="inlineStr"/>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E259" s="5" t="n">
         <v>43</v>
       </c>

--- a/output/pdf_financials_xlsx/FTS.xlsx
+++ b/output/pdf_financials_xlsx/FTS.xlsx
@@ -4745,25 +4745,25 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>0</v>
+        <v>-45</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0</v>
+        <v>-124</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="I106" s="3" t="n">
         <v>22</v>
@@ -15560,7 +15560,11 @@
           <t>Deferred income tax expense (Note 25)</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr"/>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E141" t="inlineStr">
         <is>
           <t>-</t>
@@ -17391,7 +17395,11 @@
           <t>Deferred income tax expense (Note 24)</t>
         </is>
       </c>
-      <c r="D170" t="inlineStr"/>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E170" t="inlineStr">
         <is>
           <t>-</t>
@@ -17998,7 +18006,11 @@
           <t>Deferred income tax expense (Note 23)</t>
         </is>
       </c>
-      <c r="D179" t="inlineStr"/>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E179" t="inlineStr">
         <is>
           <t>-</t>
@@ -18887,7 +18899,11 @@
           <t>Deferred income tax expense (Note 25)</t>
         </is>
       </c>
-      <c r="D192" t="inlineStr"/>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E192" t="inlineStr">
         <is>
           <t>-</t>
@@ -19370,7 +19386,11 @@
           <t>Change in non-cash operating working capital (Note 29)</t>
         </is>
       </c>
-      <c r="D199" t="inlineStr"/>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E199" t="inlineStr">
         <is>
           <t>-</t>
@@ -20361,7 +20381,11 @@
           <t>Deferred income tax expense (Note 26)</t>
         </is>
       </c>
-      <c r="D214" t="inlineStr"/>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E214" t="inlineStr">
         <is>
           <t>-</t>
@@ -20710,7 +20734,11 @@
           <t>Change in non-cash operating working capital (Note 30)</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr"/>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E219" t="inlineStr">
         <is>
           <t>-</t>
@@ -21589,7 +21617,11 @@
           <t>Deferred income tax expense (recovery) (Note 25)</t>
         </is>
       </c>
-      <c r="D232" t="inlineStr"/>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E232" t="inlineStr">
         <is>
           <t>-</t>
@@ -21727,7 +21759,11 @@
           <t>Change in non-cash operating working capital (Note 31)</t>
         </is>
       </c>
-      <c r="D234" t="inlineStr"/>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E234" t="inlineStr">
         <is>
           <t>-</t>
@@ -23036,7 +23072,11 @@
           <t>Change in non-cash operating working capital (Note 30)</t>
         </is>
       </c>
-      <c r="D253" t="inlineStr"/>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E253" t="inlineStr">
         <is>
           <t>-</t>
@@ -23586,7 +23626,11 @@
           <t>Future income taxes (Note 22)</t>
         </is>
       </c>
-      <c r="D261" t="inlineStr"/>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E261" t="inlineStr">
         <is>
           <t>-</t>
@@ -23994,7 +24038,11 @@
           <t>Change in non-cash operating working capital (Note 26)</t>
         </is>
       </c>
-      <c r="D267" t="inlineStr"/>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E267" t="inlineStr">
         <is>
           <t>-</t>
@@ -24343,7 +24391,11 @@
           <t>Future income taxes (Note 21)</t>
         </is>
       </c>
-      <c r="D272" t="inlineStr"/>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E272" s="5" t="n">
         <v>5</v>
       </c>
@@ -24412,7 +24464,11 @@
           <t>Change in non-cash operating working capital</t>
         </is>
       </c>
-      <c r="D273" t="inlineStr"/>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E273" s="5" t="n">
         <v>3</v>
       </c>
